--- a/feedback_forms/025_volunteer_experience_survey_evaluation_form--feedback_forms.xlsx
+++ b/feedback_forms/025_volunteer_experience_survey_evaluation_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Volunteer'}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'non-volunteer'}</t>
+          <t>non-volunteer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Volunteer'}</t>
+          <t>Non-Volunteer</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Once'}</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'ongoing'}</t>
+          <t>ongoing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Ongoing'}</t>
+          <t>Ongoing</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'multiple'}</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Multiple'}</t>
+          <t>Multiple</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'On-Site'}</t>
+          <t>On-Site</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'virtual'}</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Virtual'}</t>
+          <t>Virtual</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Volunteer'}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'non-volunteer'}</t>
+          <t>non-volunteer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Volunteer'}</t>
+          <t>Non-Volunteer</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'fundraising'}</t>
+          <t>fundraising</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Fundraising'}</t>
+          <t>Fundraising</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'educational'}</t>
+          <t>educational</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Educational'}</t>
+          <t>Educational</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Individual'}</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'group'}</t>
+          <t>group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Group'}</t>
+          <t>Group</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'On-Site'}</t>
+          <t>On-Site</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'virtual'}</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Virtual'}</t>
+          <t>Virtual</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
